--- a/Evaluación de Clima Laboral.xlsx
+++ b/Evaluación de Clima Laboral.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vrodriguez\Desktop\Directorio J\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52AA5E24-EC42-42DA-AA4D-E53E8DB1EEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB52291-4463-42A0-869C-6FBFFECDA11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -168,15 +168,9 @@
     <t>3</t>
   </si>
   <si>
-    <t>El buen ambiente, jovialidad y confianza</t>
-  </si>
-  <si>
     <t>comunicación</t>
   </si>
   <si>
-    <t>creo que si es obligatorio marcar reportes diarios para saber el avanzar comunicar que nos falta . y mas integracion entresubareas</t>
-  </si>
-  <si>
     <t>Presupuestos</t>
   </si>
   <si>
@@ -256,13 +250,19 @@
   </si>
   <si>
     <t>La priorización de proyectos clave con alto porcentaje de éxito de ventas y notoriedad en la industria</t>
+  </si>
+  <si>
+    <t>El buen ambiente y confianza</t>
+  </si>
+  <si>
+    <t>creo que si es obligatorio marcar reportes diarios para saber el avanzar comunicar que nos falta  y mas integracion entresubareas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -842,14 +842,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="20" customWidth="1"/>
     <col min="7" max="22" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -914,7 +914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -979,7 +979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1165,16 +1165,16 @@
         <v>38</v>
       </c>
       <c r="S5" t="s">
+        <v>67</v>
+      </c>
+      <c r="T5" t="s">
         <v>39</v>
       </c>
-      <c r="T5" t="s">
-        <v>40</v>
-      </c>
       <c r="U5" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -1227,19 +1227,19 @@
         <v>24</v>
       </c>
       <c r="R6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" t="s">
+        <v>42</v>
+      </c>
+      <c r="T6" t="s">
         <v>43</v>
       </c>
-      <c r="S6" t="s">
+      <c r="U6" t="s">
         <v>44</v>
       </c>
-      <c r="T6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U6" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
         <v>33</v>
@@ -1295,16 +1295,16 @@
         <v>24</v>
       </c>
       <c r="S7" t="s">
+        <v>46</v>
+      </c>
+      <c r="T7" t="s">
+        <v>47</v>
+      </c>
+      <c r="U7" t="s">
         <v>48</v>
       </c>
-      <c r="T7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U7" t="s">
-        <v>50</v>
-      </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -1360,16 +1360,16 @@
         <v>24</v>
       </c>
       <c r="S8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T8" t="s">
+        <v>50</v>
+      </c>
+      <c r="U8" t="s">
         <v>51</v>
       </c>
-      <c r="T8" t="s">
-        <v>52</v>
-      </c>
-      <c r="U8" t="s">
-        <v>53</v>
-      </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
         <v>33</v>
@@ -1425,16 +1425,16 @@
         <v>25</v>
       </c>
       <c r="S9" t="s">
+        <v>52</v>
+      </c>
+      <c r="T9" t="s">
+        <v>53</v>
+      </c>
+      <c r="U9" t="s">
         <v>54</v>
       </c>
-      <c r="T9" t="s">
-        <v>55</v>
-      </c>
-      <c r="U9" t="s">
-        <v>56</v>
-      </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -1490,16 +1490,16 @@
         <v>24</v>
       </c>
       <c r="S10" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" t="s">
+        <v>56</v>
+      </c>
+      <c r="U10" t="s">
         <v>57</v>
       </c>
-      <c r="T10" t="s">
-        <v>58</v>
-      </c>
-      <c r="U10" t="s">
-        <v>59</v>
-      </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
@@ -1555,16 +1555,16 @@
         <v>24</v>
       </c>
       <c r="S11" t="s">
+        <v>58</v>
+      </c>
+      <c r="T11" t="s">
+        <v>59</v>
+      </c>
+      <c r="U11" t="s">
         <v>60</v>
       </c>
-      <c r="T11" t="s">
-        <v>61</v>
-      </c>
-      <c r="U11" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
         <v>23</v>
@@ -1620,16 +1620,16 @@
         <v>24</v>
       </c>
       <c r="S12" t="s">
+        <v>61</v>
+      </c>
+      <c r="T12" t="s">
+        <v>62</v>
+      </c>
+      <c r="U12" t="s">
         <v>63</v>
       </c>
-      <c r="T12" t="s">
-        <v>64</v>
-      </c>
-      <c r="U12" t="s">
-        <v>65</v>
-      </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1646,13 +1646,13 @@
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s">
         <v>29</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>24</v>
@@ -1664,7 +1664,7 @@
         <v>38</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>25</v>
@@ -1682,16 +1682,16 @@
         <v>25</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S13" t="s">
+        <v>64</v>
+      </c>
+      <c r="T13" t="s">
+        <v>65</v>
+      </c>
+      <c r="U13" t="s">
         <v>66</v>
-      </c>
-      <c r="T13" t="s">
-        <v>67</v>
-      </c>
-      <c r="U13" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
